--- a/registers/Variation Log.xlsx
+++ b/registers/Variation Log.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VariationLog" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VariationLog" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -187,6 +187,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Setup notes</author>
+    <author>Variation Cover Sheet</author>
   </authors>
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
@@ -337,6 +338,26 @@
       <text>
         <t>THE WHOLE FORM AS JSON. Multiple lines of text, PLAIN — this is what the app reads back, so a reopened variation returns exactly as issued even if a column is renamed. Do not edit by hand. Roughly 1-3 kB per variation; the 63,999 character limit on a plain multi-line column is not close.
 Column type: Multiple lines (plain)</t>
+      </text>
+    </comment>
+    <comment ref="Z4" authorId="1" shapeId="0">
+      <text>
+        <t>Choice column: Draft, Submitted, Approved, Rejected. Set by the app — Submitted when the PDF is downloaded, the rest from the project dashboard.</t>
+      </text>
+    </comment>
+    <comment ref="AA4" authorId="1" shapeId="0">
+      <text>
+        <t>Currency (or Number, 2 decimals). The variation value ex GST, the total of its schedules of rates.</t>
+      </text>
+    </comment>
+    <comment ref="AB4" authorId="1" shapeId="0">
+      <text>
+        <t>Currency (or Number, 2 decimals). What the head contractor approved, set on the project dashboard when the status is Approved. Blank until then.</t>
+      </text>
+    </comment>
+    <comment ref="AC4" authorId="1" shapeId="0">
+      <text>
+        <t>Date only. When it was approved, set on the project dashboard. Blank until then.</t>
       </text>
     </comment>
   </commentList>
@@ -666,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -694,6 +715,10 @@
     <col width="18" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="40" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -836,6 +861,26 @@
           <t>Payload</t>
         </is>
       </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>ValueExGst</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>ApprovedValue</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>ApprovedDate</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -962,6 +1007,16 @@
           <t>{"version":1,"office":"VIC","fields":{…},"drawings":[…]}</t>
         </is>
       </c>
+      <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="n">
+        <v>2440</v>
+      </c>
+      <c r="AB5" s="4" t="n"/>
+      <c r="AC5" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">

--- a/registers/Variation Log.xlsx
+++ b/registers/Variation Log.xlsx
@@ -358,6 +358,11 @@
     <comment ref="AC4" authorId="1" shapeId="0">
       <text>
         <t>Date only. When it was approved, set on the project dashboard. Blank until then.</t>
+      </text>
+    </comment>
+    <comment ref="AD4" authorId="1" shapeId="0">
+      <text>
+        <t>Multiple lines of text, plain. The builder commentary thread from the project dashboard, as readable text, newest last. The app keeps its own copy in Payload.</t>
       </text>
     </comment>
   </commentList>
@@ -687,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -719,6 +724,7 @@
     <col width="16" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="40" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -881,6 +887,11 @@
           <t>ApprovedDate</t>
         </is>
       </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>BuilderCommentary</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1017,6 +1028,12 @@
       </c>
       <c r="AB5" s="4" t="n"/>
       <c r="AC5" s="4" t="n"/>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>24 Oct 2026, 09:15 am — Spiros Laladakis, Built (entered by Adam Donnelly):
+Approved as submitted.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">

--- a/registers/Variation Log.xlsx
+++ b/registers/Variation Log.xlsx
@@ -363,6 +363,11 @@
     <comment ref="AD4" authorId="1" shapeId="0">
       <text>
         <t>Multiple lines of text, plain. The builder commentary thread from the project dashboard, as readable text, newest last. The app keeps its own copy in Payload.</t>
+      </text>
+    </comment>
+    <comment ref="AE4" authorId="1" shapeId="0">
+      <text>
+        <t>Single line of text. The PM email the variation was issued with (from the project register's PmEmail, or typed on the cover sheet).</t>
       </text>
     </comment>
   </commentList>
@@ -692,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AE7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -725,6 +730,7 @@
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="40" customWidth="1" min="30" max="30"/>
+    <col width="32" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -892,6 +898,11 @@
           <t>BuilderCommentary</t>
         </is>
       </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>PmEmail</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1032,6 +1043,11 @@
         <is>
           <t>24 Oct 2026, 09:15 am — Spiros Laladakis, Built (entered by Adam Donnelly):
 Approved as submitted.</t>
+        </is>
+      </c>
+      <c r="AE5" s="4" t="inlineStr">
+        <is>
+          <t>adam.donnelly@axisplumbing.com.au</t>
         </is>
       </c>
     </row>

--- a/registers/Variation Log.xlsx
+++ b/registers/Variation Log.xlsx
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE7"/>
+  <dimension ref="A1:AF7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -731,6 +731,7 @@
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="40" customWidth="1" min="30" max="30"/>
     <col width="32" customWidth="1" min="31" max="31"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -903,6 +904,11 @@
           <t>PmEmail</t>
         </is>
       </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>DaySheetsText</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1048,6 +1054,11 @@
       <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>adam.donnelly@axisplumbing.com.au</t>
+        </is>
+      </c>
+      <c r="AF5" s="4" t="inlineStr">
+        <is>
+          <t>DS-014  After-hours crew, sewer relocation  approved by Spiros Laladakis</t>
         </is>
       </c>
     </row>
